--- a/miranda_Ex3A_tables.xlsx
+++ b/miranda_Ex3A_tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nataliamiranda\Documents\DATA_Labs\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681990FB-AE9A-49AC-AB80-EB83FED6FAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44685051-4EA3-4525-B9D9-E63A4A38C4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>customer_id</t>
   </si>
@@ -79,16 +79,54 @@
   </si>
   <si>
     <t>method</t>
+  </si>
+  <si>
+    <t>Maria Lopez</t>
+  </si>
+  <si>
+    <t>408-555-1234</t>
+  </si>
+  <si>
+    <t>maria.lopez@email.com</t>
+  </si>
+  <si>
+    <t>123 Main St</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>Golden Retriever</t>
+  </si>
+  <si>
+    <t>friendly energetic</t>
+  </si>
+  <si>
+    <t>09:00am</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>Card</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -123,15 +161,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -416,8 +458,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="13.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="21" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -436,16 +481,84 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{4E747C0A-FCD6-49F8-8BAB-892D30699D5B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F97D128C-5D77-4503-B636-72525E0952FF}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="3" max="3" width="15.08984375" customWidth="1"/>
+    <col min="4" max="4" width="6.54296875" customWidth="1"/>
+    <col min="5" max="5" width="15.36328125" customWidth="1"/>
     <col min="6" max="6" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -467,6 +580,23 @@
       </c>
       <c r="F1" s="2" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -476,8 +606,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D999AC-59E8-455B-9F91-817B07CED123}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="9.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -497,6 +630,33 @@
       </c>
       <c r="F1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4">
+        <v>45757</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B4">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +666,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C8E9F5-32FF-4AAD-9D60-340B88F0878E}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="12.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -526,6 +686,20 @@
         <v>16</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>25</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46122</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
